--- a/event_registration_forms/026_garden_club_meeting_attendance_form--event_registration_forms.xlsx
+++ b/event_registration_forms/026_garden_club_meeting_attendance_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_attended</t>
+          <t>meeting_attended</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Not Attended</t>
+          <t>Meeting Attended</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>meeting_attendance_2_choices</t>
+          <t>event_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>meeting_attended</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meeting Attended</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_choices</t>
+          <t>event_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>event_2_choices</t>
+          <t>event_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>event_3_choices</t>
+          <t>event_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>event_4_choices</t>
+          <t>event_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>event_5_choices</t>
+          <t>event_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>event_6_choices</t>
+          <t>event_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>event_7_choices</t>
+          <t>event_8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>event_8_choices</t>
+          <t>event_9_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>event_9_choices</t>
+          <t>event_10_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>event_10_choices</t>
+          <t>event_11_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>event_11_choices</t>
+          <t>event_12_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>event_12_choices</t>
+          <t>event_13_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>event_13_choices</t>
+          <t>event_14_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>Event 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>event_14_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>event_3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Event 3</t>
         </is>
